--- a/Matlab - Simulink/Tablas/Tabla_Sweep_Jeq_beq.xlsx
+++ b/Matlab - Simulink/Tablas/Tabla_Sweep_Jeq_beq.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
   <si>
     <t>J_eq</t>
   </si>
@@ -51,12 +51,75 @@
     <t>P2</t>
   </si>
   <si>
+    <t>-95.29159+145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775+131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961+119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292+109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586+100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337+92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439+84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814+77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409+70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182+63.77421i</t>
+  </si>
+  <si>
     <t>P3</t>
   </si>
   <si>
+    <t>-95.29159-145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775-131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961-119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292-109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586-100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337-92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439-84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814-77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409-70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182-63.77421i</t>
+  </si>
+  <si>
     <t>Cero</t>
   </si>
   <si>
+    <t>-189.5793</t>
+  </si>
+  <si>
     <t>wn_rad_s</t>
   </si>
   <si>
@@ -75,82 +138,73 @@
     <t>P2</t>
   </si>
   <si>
+    <t>-95.29159+145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775+131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961+119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292+109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586+100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337+92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439+84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814+77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409+70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182+63.77421i</t>
+  </si>
+  <si>
     <t>P3</t>
   </si>
   <si>
+    <t>-95.29159-145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775-131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961-119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292-109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586-100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337-92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439-84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814-77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409-70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182-63.77421i</t>
+  </si>
+  <si>
     <t>Cero</t>
   </si>
   <si>
-    <t>wn_rad_s</t>
-  </si>
-  <si>
-    <t>zeta</t>
-  </si>
-  <si>
-    <t>J_eq</t>
-  </si>
-  <si>
-    <t>b_eq</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Cero</t>
-  </si>
-  <si>
-    <t>wn_rad_s</t>
-  </si>
-  <si>
-    <t>zeta</t>
-  </si>
-  <si>
-    <t>J_eq</t>
-  </si>
-  <si>
-    <t>b_eq</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Cero</t>
-  </si>
-  <si>
-    <t>wn_rad_s</t>
-  </si>
-  <si>
-    <t>zeta</t>
-  </si>
-  <si>
-    <t>J_eq</t>
-  </si>
-  <si>
-    <t>b_eq</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Cero</t>
+    <t>-189.5793</t>
   </si>
   <si>
     <t>wn_rad_s</t>
@@ -208,37 +262,37 @@
     <col min="1" max="1" width="15.5703125" customWidth="true"/>
     <col min="2" max="2" width="15.5703125" customWidth="true"/>
     <col min="3" max="3" width="3.28515625" customWidth="true"/>
-    <col min="4" max="4" width="12.42578125" customWidth="true"/>
-    <col min="5" max="5" width="12.42578125" customWidth="true"/>
-    <col min="6" max="6" width="12.42578125" customWidth="true"/>
+    <col min="4" max="4" width="18.5703125" customWidth="true"/>
+    <col min="5" max="5" width="18.28515625" customWidth="true"/>
+    <col min="6" max="6" width="9.42578125" customWidth="true"/>
     <col min="7" max="7" width="11.7109375" customWidth="true"/>
     <col min="8" max="8" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>43</v>
-      </c>
       <c r="E1" s="0" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
@@ -251,14 +305,14 @@
       <c r="C2" s="0">
         <v>0</v>
       </c>
-      <c r="D2" s="0">
-        <v>-95.291585674344304</v>
-      </c>
-      <c r="E2" s="0">
-        <v>-95.291585674344304</v>
-      </c>
-      <c r="F2" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D2" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G2" s="0">
         <v>174.0907631319642</v>
@@ -277,14 +331,14 @@
       <c r="C3" s="0">
         <v>0</v>
       </c>
-      <c r="D3" s="0">
-        <v>-95.237751528441166</v>
-      </c>
-      <c r="E3" s="0">
-        <v>-95.237751528441166</v>
-      </c>
-      <c r="F3" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D3" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G3" s="0">
         <v>162.61769793641946</v>
@@ -303,14 +357,14 @@
       <c r="C4" s="0">
         <v>0</v>
       </c>
-      <c r="D4" s="0">
-        <v>-95.196100361152816</v>
-      </c>
-      <c r="E4" s="0">
-        <v>-95.196100361152816</v>
-      </c>
-      <c r="F4" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D4" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G4" s="0">
         <v>153.15245503014228</v>
@@ -329,14 +383,14 @@
       <c r="C5" s="0">
         <v>0</v>
       </c>
-      <c r="D5" s="0">
-        <v>-95.162916943577514</v>
-      </c>
-      <c r="E5" s="0">
-        <v>-95.162916943577514</v>
-      </c>
-      <c r="F5" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D5" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G5" s="0">
         <v>145.17048437682138</v>
@@ -355,14 +409,14 @@
       <c r="C6" s="0">
         <v>0</v>
       </c>
-      <c r="D6" s="0">
-        <v>-95.135857283582354</v>
-      </c>
-      <c r="E6" s="0">
-        <v>-95.135857283582354</v>
-      </c>
-      <c r="F6" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D6" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G6" s="0">
         <v>138.32099834983057</v>
@@ -381,14 +435,14 @@
       <c r="C7" s="0">
         <v>0</v>
       </c>
-      <c r="D7" s="0">
-        <v>-95.113369438819163</v>
-      </c>
-      <c r="E7" s="0">
-        <v>-95.113369438819163</v>
-      </c>
-      <c r="F7" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D7" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G7" s="0">
         <v>132.35934415348476</v>
@@ -407,14 +461,14 @@
       <c r="C8" s="0">
         <v>0</v>
       </c>
-      <c r="D8" s="0">
-        <v>-95.094385028461687</v>
-      </c>
-      <c r="E8" s="0">
-        <v>-95.094385028461687</v>
-      </c>
-      <c r="F8" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D8" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G8" s="0">
         <v>127.10899229105929</v>
@@ -433,14 +487,14 @@
       <c r="C9" s="0">
         <v>0</v>
       </c>
-      <c r="D9" s="0">
-        <v>-95.078144505824227</v>
-      </c>
-      <c r="E9" s="0">
-        <v>-95.078144505824227</v>
-      </c>
-      <c r="F9" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G9" s="0">
         <v>122.43894059080189</v>
@@ -459,14 +513,14 @@
       <c r="C10" s="0">
         <v>0</v>
       </c>
-      <c r="D10" s="0">
-        <v>-95.064093086901323</v>
-      </c>
-      <c r="E10" s="0">
-        <v>-95.064093086901323</v>
-      </c>
-      <c r="F10" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G10" s="0">
         <v>118.24965141588409</v>
@@ -485,14 +539,14 @@
       <c r="C11" s="0">
         <v>0</v>
       </c>
-      <c r="D11" s="0">
-        <v>-95.051816105888577</v>
-      </c>
-      <c r="E11" s="0">
-        <v>-95.051816105888577</v>
-      </c>
-      <c r="F11" s="0">
-        <v>-189.5793103448276</v>
+      <c r="D11" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>63</v>
       </c>
       <c r="G11" s="0">
         <v>114.46395776682166</v>

--- a/Matlab - Simulink/Tablas/Tabla_Sweep_Jeq_beq.xlsx
+++ b/Matlab - Simulink/Tablas/Tabla_Sweep_Jeq_beq.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
   <si>
     <t>J_eq</t>
   </si>
@@ -27,10 +27,160 @@
     <t>P2</t>
   </si>
   <si>
+    <t>-95.29159+145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775+131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961+119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292+109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586+100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337+92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439+84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814+77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409+70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182+63.77421i</t>
+  </si>
+  <si>
     <t>P3</t>
   </si>
   <si>
+    <t>-95.29159-145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775-131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961-119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292-109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586-100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337-92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439-84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814-77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409-70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182-63.77421i</t>
+  </si>
+  <si>
     <t>Cero</t>
+  </si>
+  <si>
+    <t>-189.5793</t>
+  </si>
+  <si>
+    <t>wn_rad_s</t>
+  </si>
+  <si>
+    <t>zeta</t>
+  </si>
+  <si>
+    <t>J_eq</t>
+  </si>
+  <si>
+    <t>b_eq</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>-95.29159+145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775+131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961+119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292+109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586+100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337+92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439+84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814+77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409+70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182+63.77421i</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>-95.29159-145.6953i</t>
+  </si>
+  <si>
+    <t>-95.23775-131.8116i</t>
+  </si>
+  <si>
+    <t>-95.1961-119.9724i</t>
+  </si>
+  <si>
+    <t>-95.16292-109.6289i</t>
+  </si>
+  <si>
+    <t>-95.13586-100.4085i</t>
+  </si>
+  <si>
+    <t>-95.11337-92.04587i</t>
+  </si>
+  <si>
+    <t>-95.09439-84.34307i</t>
+  </si>
+  <si>
+    <t>-95.07814-77.14558i</t>
+  </si>
+  <si>
+    <t>-95.06409-70.32637i</t>
+  </si>
+  <si>
+    <t>-95.05182-63.77421i</t>
+  </si>
+  <si>
+    <t>Cero</t>
+  </si>
+  <si>
+    <t>-189.5793</t>
   </si>
   <si>
     <t>wn_rad_s</t>
@@ -271,28 +421,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
@@ -306,13 +456,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G2" s="0">
         <v>174.0907631319642</v>
@@ -332,13 +482,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G3" s="0">
         <v>162.61769793641946</v>
@@ -358,13 +508,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G4" s="0">
         <v>153.15245503014228</v>
@@ -384,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G5" s="0">
         <v>145.17048437682138</v>
@@ -410,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G6" s="0">
         <v>138.32099834983057</v>
@@ -436,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G7" s="0">
         <v>132.35934415348476</v>
@@ -462,13 +612,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G8" s="0">
         <v>127.10899229105929</v>
@@ -488,13 +638,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G9" s="0">
         <v>122.43894059080189</v>
@@ -514,13 +664,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G10" s="0">
         <v>118.24965141588409</v>
@@ -540,13 +690,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="G11" s="0">
         <v>114.46395776682166</v>
